--- a/events/Poznan_2009_WC/Poznan_2009_WC_Results.xlsx
+++ b/events/Poznan_2009_WC/Poznan_2009_WC_Results.xlsx
@@ -3407,11 +3407,6 @@
           <t>1:41.731</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4887,11 +4882,6 @@
           <t>1:54.085</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7002,11 +6992,6 @@
           <t>1:33.668</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
-        <is>
-          <t>93338</t>
-        </is>
-      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>35416</t>
@@ -8202,11 +8187,6 @@
           <t>1:31.953</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8267,11 +8247,6 @@
           <t>1:33.569</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr">
-        <is>
-          <t>119523</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15536,11 +15511,6 @@
           <t>4:01.107</t>
         </is>
       </c>
-      <c r="R240" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -18699,11 +18669,6 @@
           <t>3:20.139</t>
         </is>
       </c>
-      <c r="S291" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -22177,11 +22142,6 @@
           <t>2:58.254</t>
         </is>
       </c>
-      <c r="R346" t="inlineStr">
-        <is>
-          <t>93338</t>
-        </is>
-      </c>
       <c r="S346" t="inlineStr">
         <is>
           <t>63610</t>
@@ -23997,11 +23957,6 @@
           <t>1:47.207</t>
         </is>
       </c>
-      <c r="R374" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -27421,11 +27376,6 @@
           <t>2:00.088</t>
         </is>
       </c>
-      <c r="R429" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -30041,11 +29991,6 @@
           <t>1:33.391</t>
         </is>
       </c>
-      <c r="S471" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -30726,11 +30671,6 @@
           <t>1:35.797</t>
         </is>
       </c>
-      <c r="R482" t="inlineStr">
-        <is>
-          <t>93338</t>
-        </is>
-      </c>
       <c r="S482" t="inlineStr">
         <is>
           <t>35416</t>
@@ -30921,11 +30861,6 @@
           <t>1:43.097</t>
         </is>
       </c>
-      <c r="R485" t="inlineStr">
-        <is>
-          <t>119523</t>
-        </is>
-      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -37095,11 +37030,6 @@
           <t>4:00.909</t>
         </is>
       </c>
-      <c r="R584" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -40499,11 +40429,6 @@
           <t>3:19.869</t>
         </is>
       </c>
-      <c r="S639" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -42668,11 +42593,6 @@
           <t>2:57.579</t>
         </is>
       </c>
-      <c r="R673" t="inlineStr">
-        <is>
-          <t>93338</t>
-        </is>
-      </c>
       <c r="S673" t="inlineStr">
         <is>
           <t>63610</t>
@@ -50207,11 +50127,6 @@
           <t>1:44.561</t>
         </is>
       </c>
-      <c r="R788" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -50914,11 +50829,6 @@
           <t>1:35.432</t>
         </is>
       </c>
-      <c r="R799" t="inlineStr">
-        <is>
-          <t>93338</t>
-        </is>
-      </c>
       <c r="S799" t="inlineStr">
         <is>
           <t>35416</t>
@@ -51961,11 +51871,6 @@
           <t>3:59.590</t>
         </is>
       </c>
-      <c r="R815" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -53255,11 +53160,6 @@
           <t>3:17.917</t>
         </is>
       </c>
-      <c r="S835" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -55067,11 +54967,6 @@
       <c r="P862" t="inlineStr">
         <is>
           <t>2:58.877</t>
-        </is>
-      </c>
-      <c r="R862" t="inlineStr">
-        <is>
-          <t>93338</t>
         </is>
       </c>
       <c r="S862" t="inlineStr">
@@ -63725,7 +63620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63863,61 +63758,61 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>126240</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Scotty</t>
+          <t>Jana</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BICKNELL</t>
+          <t>BLAHOVA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>126240</t>
+          <t>52232</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jana</t>
+          <t>Sergey</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLAHOVA</t>
+          <t>BORZOV</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>52232</t>
+          <t>63610</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sergey</t>
+          <t>Stephane</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BORZOV</t>
+          <t>BOULANGER</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -63929,17 +63824,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>63610</t>
+          <t>35925</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stephane</t>
+          <t>Bram</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BOULANGER</t>
+          <t>BRANDJES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -63951,17 +63846,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>35925</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bram</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BRANDJES</t>
+          <t>BRENDEL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -63973,61 +63868,61 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>35698</t>
+          <t>52150</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Jo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BRENDEL</t>
+          <t>BRIGDEN-JONES</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>52150</t>
+          <t>42447</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jo</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BRIGDEN-JONES</t>
+          <t>BRYANT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>119523</t>
+          <t>35296</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Guillaume</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BROWN</t>
+          <t>BURGER</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -64039,61 +63934,61 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>142729</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BRYANT</t>
+          <t>BURKE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>35296</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Guillaume</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BURGER</t>
+          <t>CARRINGTON</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>142729</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BURKE</t>
+          <t>CAWTHORN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -64105,39 +64000,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>36282</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CARRINGTON</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>41785</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Olivier</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CAUWENBERGH</t>
+          <t>COCHRANE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -64149,39 +64044,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>35813</t>
+          <t>36729</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Valentin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CAWTHORN</t>
+          <t>DEMYANENKO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>45846</t>
+          <t>42571</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Alexey</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>DERGUNOV</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -64193,39 +64088,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>42449</t>
+          <t>35700</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>COCHRANE</t>
+          <t>DIETZE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>36729</t>
+          <t>47253</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Valentin</t>
+          <t>Liviu Alexandru</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DEMYANENKO</t>
+          <t>DUMITRESCU LAZAR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -64237,17 +64132,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alexey</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DERGUNOV</t>
+          <t>DVORAK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -64259,17 +64154,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>35700</t>
+          <t>42337</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Henriette Engel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DIETZE</t>
+          <t>HANSEN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -64281,17 +64176,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>47253</t>
+          <t>36450</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Liviu Alexandru</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DUMITRESCU LAZAR</t>
+          <t>FERNANDES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -64303,39 +64198,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>42453</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DVORAK</t>
+          <t>FOURNEL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>36457</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Henriette Engel</t>
+          <t>Beatriz</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HANSEN</t>
+          <t>GOMES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -64347,17 +64242,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>35318</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FERNANDES</t>
+          <t>GOUBEL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -64369,61 +64264,61 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>35705</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FOURNEL</t>
+          <t>GROSS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>36457</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Beatriz</t>
+          <t>Marcin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GOMES</t>
+          <t>GRZYBOWSKI</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>35318</t>
+          <t>44428</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Lubomir</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GOUBEL</t>
+          <t>HAGARA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -64435,39 +64330,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>35705</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GROSS</t>
+          <t>HANNAH</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>42042</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Dzianis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GRZYBOWSKI</t>
+          <t>HARAZHA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -64479,83 +64374,83 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>44428</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lubomir</t>
+          <t>Bridgitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HAGARA</t>
+          <t>HARTLEY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>64492</t>
+          <t>36283</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Teneale</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HALL</t>
+          <t>HATTON</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HANNAH</t>
+          <t>HOFF</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>35708</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dzianis</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HARAZHA</t>
+          <t>HOLLSTEIN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -64567,39 +64462,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>36391</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bridgitte</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HARTLEY</t>
+          <t>HOLTZ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>52174</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Teneale</t>
+          <t>Jieyi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HATTON</t>
+          <t>HUANG</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -64611,17 +64506,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>35323</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Etienne</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HOFF</t>
+          <t>HUBERT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -64633,17 +64528,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>35708</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Gabor</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HOLLSTEIN</t>
+          <t>JAKUBIK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -64655,17 +64550,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>35709</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Sebastien</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HOLTZ</t>
+          <t>JOUVE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -64677,83 +64572,83 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>52174</t>
+          <t>35874</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jieyi</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HUANG</t>
+          <t>KACZOR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>35323</t>
+          <t>45330</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>Shiho</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HUBERT</t>
+          <t>KAKIZAKI</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>44425</t>
+          <t>44421</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gabor</t>
+          <t>Ivana</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JAKUBIK</t>
+          <t>KMETOVA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sebastien</t>
+          <t>Gerasim</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>JOUVE</t>
+          <t>KOCHNEV</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -64765,17 +64660,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>47717</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Rastislav</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KACZOR</t>
+          <t>KOHUT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -64787,61 +64682,61 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>45330</t>
+          <t>35937</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shiho</t>
+          <t>Arkadiusz</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KAKIZAKI</t>
+          <t>KRAJEWSKI</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>44421</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ivana</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KMETOVA</t>
+          <t>KUJAWSKI</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>47675</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gerasim</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KOCHNEV</t>
+          <t>KULETA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -64853,17 +64748,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>47717</t>
+          <t>61246</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rastislav</t>
+          <t>Pierre-Luc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KOHUT</t>
+          <t>LALIBERTE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -64875,39 +64770,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>46232</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Arkadiusz</t>
+          <t>Irina</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KRAJEWSKI</t>
+          <t>LAURIC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>35880</t>
+          <t>42257</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mariusz</t>
+          <t>Andres</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KUJAWSKI</t>
+          <t>LAZO</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -64919,17 +64814,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>35380</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KULETA</t>
+          <t>LECRUBIER</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -64941,127 +64836,127 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>61246</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pierre-Luc</t>
+          <t>Ana-Roxana</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LALIBERTE</t>
+          <t>LEHACI</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>46232</t>
+          <t>35719</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Irina</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LAURIC</t>
+          <t>LEUE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>35984</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Andres</t>
+          <t>Agnes</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LAZO</t>
+          <t>BRUN-LIE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>35380</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Vincent</t>
+          <t>Una Helen Bean</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LECRUBIER</t>
+          <t>LOUNDER</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>36389</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ana-Roxana</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LEHACI</t>
+          <t>LOUW</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>35719</t>
+          <t>43664</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Serguey</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LEUE</t>
+          <t>TORRES MADRIGAL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -65073,39 +64968,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>35984</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Agnes</t>
+          <t>Rafal</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BRUN-LIE</t>
+          <t>MARON</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>42461</t>
+          <t>36224</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Una Helen Bean</t>
+          <t>Hayleigh-Jayne</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LOUNDER</t>
+          <t>MASON</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -65117,17 +65012,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>36389</t>
+          <t>36226</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LOUW</t>
+          <t>MCKEEVER</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -65139,17 +65034,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>93338</t>
+          <t>47673</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jean-Baptiste</t>
+          <t>Vadim</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HERPERS</t>
+          <t>MENKOV</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -65161,17 +65056,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>43664</t>
+          <t>47252</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Serguey</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TORRES MADRIGAL</t>
+          <t>MIHALACHI</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -65183,17 +65078,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>35928</t>
+          <t>52229</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rafal</t>
+          <t>Serik</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MARON</t>
+          <t>MIRBEKOV</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -65205,61 +65100,61 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>42465</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Hayleigh-Jayne</t>
+          <t>Angus</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MASON</t>
+          <t>MORTIMER</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>36226</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MCKEEVER</t>
+          <t>NAJA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>47673</t>
+          <t>65873</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vadim</t>
+          <t>Traian</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MENKOV</t>
+          <t>NEAGU</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -65271,17 +65166,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>47252</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Ricardas</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MIHALACHI</t>
+          <t>NEKRIOSIUS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -65293,17 +65188,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>52229</t>
+          <t>35723</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Serik</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MIRBEKOV</t>
+          <t>NUCK</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -65315,61 +65210,61 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>45329</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Angus</t>
+          <t>Asumi</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MORTIMER</t>
+          <t>OHMURA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>35557</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Mark William</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NAJA</t>
+          <t>OLDERSHAW</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>65873</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Traian</t>
+          <t>Andrej</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NEAGU</t>
+          <t>OLIJNIK</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -65381,39 +65276,39 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>42467</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ricardas</t>
+          <t>Genevieve Wendy Susan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NEKRIOSIUS</t>
+          <t>ORTON</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>35723</t>
+          <t>41784</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NUCK</t>
+          <t>PANNECOUCKE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -65425,39 +65320,39 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>45329</t>
+          <t>41991</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Asumi</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OHMURA</t>
+          <t>PIATRUSHENKA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mark William</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OLDERSHAW</t>
+          <t>PIMENTA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -65469,17 +65364,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>53954</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Andrej</t>
+          <t>Bartosz</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>OLIJNIK</t>
+          <t>PLAWSKI</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -65491,17 +65386,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>42467</t>
+          <t>36455</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Genevieve Wendy Susan</t>
+          <t>Teresa</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ORTON</t>
+          <t>PORTELA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -65513,17 +65408,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>41784</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Rene Holten</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PANNECOUCKE</t>
+          <t>POULSEN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -65535,17 +65430,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>41991</t>
+          <t>42052</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Dzmitry</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PIATRUSHENKA</t>
+          <t>RABCHANKA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -65557,17 +65452,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>36448</t>
+          <t>35549</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Jaroslav</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PIMENTA</t>
+          <t>RADON</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -65579,17 +65474,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>53954</t>
+          <t>35724</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PLAWSKI</t>
+          <t>RAUHE</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -65601,39 +65496,39 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>36455</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Teresa</t>
+          <t>Brady Daniel Heim</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PORTELA</t>
+          <t>REARDON</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>42336</t>
+          <t>35725</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Rene Holten</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>POULSEN</t>
+          <t>REBSTOCK</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -65645,39 +65540,39 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>42052</t>
+          <t>36456</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dzmitry</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>RABCHANKA</t>
+          <t>RODRIGUES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>35549</t>
+          <t>44427</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jaroslav</t>
+          <t>Matej</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RADON</t>
+          <t>RUSNAK</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -65689,17 +65584,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>35724</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>RAUHE</t>
+          <t>SALBU</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -65711,17 +65606,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>42468</t>
+          <t>175299</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Brady Daniel Heim</t>
+          <t>Abbas</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>REARDON</t>
+          <t>SAYADI KACHALAKI</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -65733,39 +65628,39 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>35725</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Yvonne</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>REBSTOCK</t>
+          <t>SCHURING</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Viktoria</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>RODRIGUES</t>
+          <t>SCHWARZ</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -65777,61 +65672,61 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>44427</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Matej</t>
+          <t>Natalya</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>RUSNAK</t>
+          <t>SERGEYEVA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>56337</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Ekaterina</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SALBU</t>
+          <t>SHUBINA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>175299</t>
+          <t>35858</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Abbas</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SAYADI KACHALAKI</t>
+          <t>SIEMIONOWSKI</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -65843,105 +65738,105 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Yvonne</t>
+          <t>Emanuel</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SCHURING</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>35409</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Viktoria</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SCHWARZ</t>
+          <t>SIMART</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>42573</t>
+          <t>42341</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Natalya</t>
+          <t>Emil Staer</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SERGEYEVA</t>
+          <t>SIMENSEN</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>56337</t>
+          <t>35776</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ekaterina</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SHUBINA</t>
+          <t>STERBA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>35858</t>
+          <t>45793</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SIEMIONOWSKI</t>
+          <t>STEWART</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -65953,17 +65848,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>36449</t>
+          <t>36792</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Emanuel</t>
+          <t>Jevgenij</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>SHUKLIN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -65975,17 +65870,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>35409</t>
+          <t>35550</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SIMART</t>
+          <t>SVAB</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -65997,17 +65892,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>42341</t>
+          <t>53107</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Emil Staer</t>
+          <t>Tamas</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SIMENSEN</t>
+          <t>SZALAI</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -66019,17 +65914,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>35776</t>
+          <t>41549</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>STERBA</t>
+          <t>TOTH</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -66041,39 +65936,39 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>35414</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>STEWART</t>
+          <t>TROEL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>36792</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Jevgenij</t>
+          <t>Quentin</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SHUKLIN</t>
+          <t>URBAN</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -66085,17 +65980,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>35550</t>
+          <t>42054</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Dzmitry</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SVAB</t>
+          <t>VAITSISHKIN</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -66107,17 +66002,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>53107</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tamas</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SZALAI</t>
+          <t>VAN KOEVERDEN</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -66129,7 +66024,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>41549</t>
+          <t>47429</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -66139,7 +66034,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TOTH</t>
+          <t>VARGA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -66151,105 +66046,105 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>35414</t>
+          <t>42053</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Aliaksandr</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TROEL</t>
+          <t>VAUCHETSKI</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Quentin</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>URBAN</t>
+          <t>WALCZYKIEWICZ</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>42054</t>
+          <t>36222</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Dzmitry</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VAITSISHKIN</t>
+          <t>WALKER</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>35733</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Conny</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VAN KOEVERDEN</t>
+          <t>WASSMUTH</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>47429</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>VARGA</t>
+          <t>WATKINS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -66261,39 +66156,39 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>42053</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Aliaksandr</t>
+          <t>Ewelina</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>VAUCHETSKI</t>
+          <t>WOJNAROWSKA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>69210</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>WALCZYKIEWICZ</t>
+          <t>WRIGHT</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -66305,174 +66200,64 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>36222</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>WALKER</t>
+          <t>WYLENZEK</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Conny</t>
+          <t>Alexandr</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>WASSMUTH</t>
+          <t>YEMELYANOV</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>37764</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Nejc</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>WATKINS</t>
+          <t>ZNIDARCIC</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>35558</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Ewelina</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>WOJNAROWSKA</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>69210</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Emily</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>WRIGHT</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>35737</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>WYLENZEK</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>42567</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Alexandr</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>YEMELYANOV</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>37764</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Nejc</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>ZNIDARCIC</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Poznan_2009_WC/Poznan_2009_WC_Results.xlsx
+++ b/events/Poznan_2009_WC/Poznan_2009_WC_Results.xlsx
@@ -1342,6 +1342,11 @@
           <t>36455</t>
         </is>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>36457</t>
@@ -6127,6 +6132,11 @@
           <t>1:58.286</t>
         </is>
       </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7437,6 +7447,11 @@
           <t>41549</t>
         </is>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>41548</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7877,6 +7892,11 @@
           <t>1:35.349</t>
         </is>
       </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8247,6 +8267,11 @@
           <t>1:33.569</t>
         </is>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>36229</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11737,6 +11762,11 @@
           <t>3:32.448</t>
         </is>
       </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12672,6 +12702,11 @@
           <t>3:37.055</t>
         </is>
       </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13602,6 +13637,11 @@
           <t>3:34.741</t>
         </is>
       </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>35299</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -15951,6 +15991,11 @@
           <t>4:08.927</t>
         </is>
       </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -16141,6 +16186,11 @@
           <t>4:08.871</t>
         </is>
       </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -19343,6 +19393,11 @@
           <t>3:26.205</t>
         </is>
       </c>
+      <c r="R302" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -22802,6 +22857,11 @@
           <t>41549</t>
         </is>
       </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>41548</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -26811,6 +26871,11 @@
           <t>1:57.910</t>
         </is>
       </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -28796,6 +28861,11 @@
           <t>1:57.325</t>
         </is>
       </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -30296,6 +30366,11 @@
           <t>41549</t>
         </is>
       </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>41548</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -30861,6 +30936,11 @@
           <t>1:43.097</t>
         </is>
       </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>36229</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -31286,6 +31366,11 @@
           <t>1:36.888</t>
         </is>
       </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -34246,6 +34331,11 @@
           <t>3:37.219</t>
         </is>
       </c>
+      <c r="R539" t="inlineStr">
+        <is>
+          <t>35299</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -34306,6 +34396,11 @@
           <t>3:38.283</t>
         </is>
       </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -35611,6 +35706,11 @@
           <t>3:41.401</t>
         </is>
       </c>
+      <c r="R561" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -36900,6 +37000,11 @@
       <c r="L582" t="n">
         <v>1</v>
       </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
       <c r="X582" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -38325,6 +38430,11 @@
           <t>4:11.530</t>
         </is>
       </c>
+      <c r="R605" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -40679,6 +40789,11 @@
           <t>3:31.177</t>
         </is>
       </c>
+      <c r="R643" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -42738,6 +42853,11 @@
           <t>41549</t>
         </is>
       </c>
+      <c r="U675" t="inlineStr">
+        <is>
+          <t>41548</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -43211,6 +43331,11 @@
           <t>36455</t>
         </is>
       </c>
+      <c r="T682" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
       <c r="U682" t="inlineStr">
         <is>
           <t>36457</t>
@@ -45114,6 +45239,11 @@
           <t>1:56.924</t>
         </is>
       </c>
+      <c r="R711" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -47996,6 +48126,11 @@
           <t>1:55.703</t>
         </is>
       </c>
+      <c r="R755" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -50963,6 +51098,11 @@
           <t>41549</t>
         </is>
       </c>
+      <c r="S801" t="inlineStr">
+        <is>
+          <t>41548</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -51484,6 +51624,11 @@
           <t>3:34.962</t>
         </is>
       </c>
+      <c r="R809" t="inlineStr">
+        <is>
+          <t>35299</t>
+        </is>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -51608,6 +51753,11 @@
           <t>3:42.618</t>
         </is>
       </c>
+      <c r="R811" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -58864,6 +59014,11 @@
           <t>3:37.117</t>
         </is>
       </c>
+      <c r="R922" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -59356,6 +59511,11 @@
           <t>18:33.31</t>
         </is>
       </c>
+      <c r="R930" t="inlineStr">
+        <is>
+          <t>35299</t>
+        </is>
+      </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
@@ -60652,6 +60812,11 @@
           <t>122</t>
         </is>
       </c>
+      <c r="R952" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
       <c r="X952" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -63324,6 +63489,11 @@
       <c r="P997" t="inlineStr">
         <is>
           <t>23:34.80</t>
+        </is>
+      </c>
+      <c r="R997" t="inlineStr">
+        <is>
+          <t>52756</t>
         </is>
       </c>
     </row>
@@ -63620,7 +63790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66263,6 +66433,182 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>35299</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Cyrille</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>CARRE</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>36229</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SCHOFIELD</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>BOYTON</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>36459</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Joana</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SOUSA</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>41548</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PAUMAN</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>HORNSBY</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Shahou</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>NASERI</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Poznan_2009_WC/Poznan_2009_WC_Results.xlsx
+++ b/events/Poznan_2009_WC/Poznan_2009_WC_Results.xlsx
@@ -3412,6 +3412,11 @@
           <t>1:41.731</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>41785</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4887,6 +4892,11 @@
           <t>1:54.085</t>
         </is>
       </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>64492</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8207,6 +8217,11 @@
           <t>1:31.953</t>
         </is>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8267,6 +8282,11 @@
           <t>1:33.569</t>
         </is>
       </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>119523</t>
+        </is>
+      </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>36229</t>
@@ -15551,6 +15571,11 @@
           <t>4:01.107</t>
         </is>
       </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>64492</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -18719,6 +18744,11 @@
           <t>3:20.139</t>
         </is>
       </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -24017,6 +24047,11 @@
           <t>1:47.207</t>
         </is>
       </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>41785</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -27441,6 +27476,11 @@
           <t>2:00.088</t>
         </is>
       </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>64492</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -30061,6 +30101,11 @@
           <t>1:33.391</t>
         </is>
       </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -30936,6 +30981,11 @@
           <t>1:43.097</t>
         </is>
       </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>119523</t>
+        </is>
+      </c>
       <c r="S485" t="inlineStr">
         <is>
           <t>36229</t>
@@ -37135,6 +37185,11 @@
           <t>4:00.909</t>
         </is>
       </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>64492</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -40539,6 +40594,11 @@
           <t>3:19.869</t>
         </is>
       </c>
+      <c r="S639" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -50262,6 +50322,11 @@
           <t>1:44.561</t>
         </is>
       </c>
+      <c r="R788" t="inlineStr">
+        <is>
+          <t>41785</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -52021,6 +52086,11 @@
           <t>3:59.590</t>
         </is>
       </c>
+      <c r="R815" t="inlineStr">
+        <is>
+          <t>64492</t>
+        </is>
+      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -53308,6 +53378,11 @@
       <c r="P835" t="inlineStr">
         <is>
           <t>3:17.917</t>
+        </is>
+      </c>
+      <c r="S835" t="inlineStr">
+        <is>
+          <t>51822</t>
         </is>
       </c>
     </row>
@@ -63790,7 +63865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D128"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66609,6 +66684,94 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>41785</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Olivier</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CAUWENBERGH</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Scotty</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>BICKNELL</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>64492</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>HALL</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>119523</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Ben</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>BROWN</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Poznan_2009_WC/Poznan_2009_WC_Results.xlsx
+++ b/events/Poznan_2009_WC/Poznan_2009_WC_Results.xlsx
@@ -3412,11 +3412,6 @@
           <t>1:41.731</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4892,11 +4887,6 @@
           <t>1:54.085</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8217,11 +8207,6 @@
           <t>1:31.953</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -15571,11 +15556,6 @@
           <t>4:01.107</t>
         </is>
       </c>
-      <c r="R240" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -18744,11 +18724,6 @@
           <t>3:20.139</t>
         </is>
       </c>
-      <c r="S291" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -24047,11 +24022,6 @@
           <t>1:47.207</t>
         </is>
       </c>
-      <c r="R374" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -27476,11 +27446,6 @@
           <t>2:00.088</t>
         </is>
       </c>
-      <c r="R429" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -30101,11 +30066,6 @@
           <t>1:33.391</t>
         </is>
       </c>
-      <c r="S471" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -37185,11 +37145,6 @@
           <t>4:00.909</t>
         </is>
       </c>
-      <c r="R584" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -40594,11 +40549,6 @@
           <t>3:19.869</t>
         </is>
       </c>
-      <c r="S639" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -50322,11 +50272,6 @@
           <t>1:44.561</t>
         </is>
       </c>
-      <c r="R788" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -52086,11 +52031,6 @@
           <t>3:59.590</t>
         </is>
       </c>
-      <c r="R815" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -53378,11 +53318,6 @@
       <c r="P835" t="inlineStr">
         <is>
           <t>3:17.917</t>
-        </is>
-      </c>
-      <c r="S835" t="inlineStr">
-        <is>
-          <t>51822</t>
         </is>
       </c>
     </row>
@@ -63865,7 +63800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66687,86 +66622,20 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>41785</t>
+          <t>119523</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Olivier</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CAUWENBERGH</t>
+          <t>BROWN</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Scotty</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>BICKNELL</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Thomas</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>HALL</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>119523</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Ben</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>BROWN</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Poznan_2009_WC/Poznan_2009_WC_Results.xlsx
+++ b/events/Poznan_2009_WC/Poznan_2009_WC_Results.xlsx
@@ -8267,11 +8267,6 @@
           <t>1:33.569</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr">
-        <is>
-          <t>119523</t>
-        </is>
-      </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>36229</t>
@@ -30939,11 +30934,6 @@
       <c r="P485" t="inlineStr">
         <is>
           <t>1:43.097</t>
-        </is>
-      </c>
-      <c r="R485" t="inlineStr">
-        <is>
-          <t>119523</t>
         </is>
       </c>
       <c r="S485" t="inlineStr">
@@ -63800,7 +63790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66619,28 +66609,6 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>119523</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Ben</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>BROWN</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Poznan_2009_WC/Poznan_2009_WC_Results.xlsx
+++ b/events/Poznan_2009_WC/Poznan_2009_WC_Results.xlsx
@@ -8147,6 +8147,11 @@
           <t>41991</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>42044</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -22647,6 +22652,11 @@
           <t>41991</t>
         </is>
       </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>42044</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -31006,6 +31016,11 @@
           <t>41991</t>
         </is>
       </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>42044</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -45507,6 +45522,11 @@
           <t>41991</t>
         </is>
       </c>
+      <c r="S715" t="inlineStr">
+        <is>
+          <t>42044</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -54921,6 +54941,11 @@
       <c r="R859" t="inlineStr">
         <is>
           <t>41991</t>
+        </is>
+      </c>
+      <c r="U859" t="inlineStr">
+        <is>
+          <t>42044</t>
         </is>
       </c>
     </row>
@@ -63790,7 +63815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D128"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66609,6 +66634,28 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>42044</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Vadzim</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>MAKHNEV</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Poznan_2009_WC/Poznan_2009_WC_Results.xlsx
+++ b/events/Poznan_2009_WC/Poznan_2009_WC_Results.xlsx
@@ -4517,6 +4517,11 @@
           <t>1:54.504</t>
         </is>
       </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -15001,6 +15006,11 @@
       <c r="L231" t="n">
         <v>1</v>
       </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
       <c r="X231" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -26636,6 +26646,11 @@
           <t>1:54.122</t>
         </is>
       </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -44731,6 +44746,11 @@
       <c r="P703" t="inlineStr">
         <is>
           <t>2:01.725</t>
+        </is>
+      </c>
+      <c r="R703" t="inlineStr">
+        <is>
+          <t>36633</t>
         </is>
       </c>
     </row>
@@ -63815,7 +63835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66656,6 +66676,28 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>NIVALTER</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>DOS SANTOS JESUS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
